--- a/holded_reviews.xlsx
+++ b/holded_reviews.xlsx
@@ -1,57 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reviews" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviews" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <sz val="11"/>
+      <color rgb="00C0392B"/>
     </font>
   </fonts>
   <fills count="2">
@@ -71,51 +60,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -188,41 +157,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -230,1057 +199,1254 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="4" min="1" max="1"/>
-    <col width="34" customWidth="1" style="4" min="2" max="2"/>
-    <col width="30" customWidth="1" style="4" min="3" max="3"/>
-    <col width="60" customWidth="1" style="4" min="4" max="4"/>
-    <col width="16" customWidth="1" style="4" min="5" max="5"/>
-    <col width="22" customWidth="1" style="4" min="6" max="6"/>
-    <col width="8" customWidth="1" style="4" min="7" max="7"/>
-    <col width="45" customWidth="1" style="4" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>GUID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Titulo</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pais</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="5">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>e4e97f8db2cabae0d9cda9fc2ac77adf</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>That was all new for me</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>That was all new for me, but I learned a lot! Thanks :)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Grewal Sardarni</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6a4cdf247df6fa1806c446b0</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="64.90000000000001" customHeight="1" s="5">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>0f8fcc1c5e971eabdc5229738f1ccee7</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>brilliant</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>at first my topic was handed to an AI operator. worked fine. when the problem seemed more detailed I immediately got two very nice and attending real humans that took care of my problem until it was solved. Eunice and Judith! friendly, and super fast! brilliant!</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Daniel</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6a0c2e719888049b8e32ef09</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>1483317738cb2dfe0593f828be959638</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Everything about this company is the…</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Everything about this company is the best,the best of the best</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Ola</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/69dec7a1109e2d50fb0d04fc</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="153.7" customHeight="1" s="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>8c8b06d796061c1e850bbec0afc7d825</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Customer support = radio silence</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Used it for over 2 years now, functionality is limited, price is fine, but I rather pay a little more and get a better solution. Once you run into an issue, do not expect customer support to step in, radio silence. 
-They do not offer e-facturation yet for businesses that have an e-commerce store. What if you have B2C and B2B clients? too bad, no solution. They do not even allow you to correctly track stock across markets if you have several warehouses with the same product. It just substracts it from the default warehouse.
-Looking to switch asap to other alternatives.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Used it for over 2 years now, functionality is limited, price is fine, but I rather pay a little more and get a better solution. Once you run into an issue, do not expect customer support to step in, radio silence. They do not offer e-facturation yet for businesses that have an e-commerce store. What if you have B2C and B2B clients? too bad, no solution. They do not even allow you to correctly track stock across markets if you have several warehouses with the same product. It just substracts it from the default warehouse. Looking to switch asap to other alternatives.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Alex De Cort</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Facturación</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6989ff61f320d80b98f056e3</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="128.35" customHeight="1" s="5">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>6cdc64568a4ff7353dd7e3c46c4761e3</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Customer Service Very Slow</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>I have emailed, opened support tickets, called and used their chat - ZERO replies or customer support for over two weeks now. This is appalling.
-+++edit 02/12/2025 +++ finally got all the answer I needed and quick friendly support today. It has been over two weeks though and it has been difficult to get support before. However, I like the portal itself very much, it works very well. And they deserve a better rating after reaching out to me today, so upgrade to three stars and if their service improves absolutely five.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>I have emailed, opened support tickets, called and used their chat - ZERO replies or customer support for over two weeks now. This is appalling. +++edit 02/12/2025 +++ finally got all the answer I needed and quick friendly support today. It has been over two weeks though and it has been difficult to get support before. However, I like the portal itself very much, it works very well. And they deserve a better rating after reaching out to me today, so upgrade to three stars and if their service improves absolutely five.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>3/5 (Average)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Marc</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/692dbc5f9052938aee6f19d7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="39.55" customHeight="1" s="5">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>c5d43d6d93e94baee100a71d5bedcd01</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>This is a professional company w a…</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>This is a professional company w a perfect system to work with. The layout of the program is built logically and the in the chat they are also extremely helpful. Thank you Marisa! ☺️</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>This is a professional company w a perfect system to work with. The layout of the program is built logically and the in the chat they are also extremely helpful. Thank you Marisa!</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Bulcs</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6924204e161ac50d76378d16</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90.25" customHeight="1" s="5">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>a1353eb2394ab3db064a6c76dd096cbf</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Really poor service and blocking the basic plan!</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Really poor service. 
-Trying to set up a plan and it always force you to take something more expensive than what you need.
-when you want to explain it... the AI agent just drives you crazy repeating the same.
-impossible to talk to a real person. 
-Really don't recommend to choose Holded.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Really poor service. Trying to set up a plan and it always force you to take something more expensive than what you need. when you want to explain it... the AI agent just drives you crazy repeating the same. impossible to talk to a real person. Really don't recommend to choose Holded.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Jean Louis Guisset</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/690c85f3c3bd5399a98cc1ee</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="280.55" customHeight="1" s="5">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>c1a0e7a96758149335f62f4a521ddbca</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>This software is the worst part of my job</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>This software is the worst part of my job, i resent it so much that i make sure that invoice and expense as little as possible just to avoid using it.
-Reconciling anything in a currency that differs from the current that my bank account is in is an utter pain. 
-All my expenses are in dollars, but my account is in euros.
-This software is expensive and costs me days every month in which I should be doing my actual job/trade.
-Worst of all, migrating away from it looks like it is going to cost me days. 
-Any features that look like they would save you any time are always on the next paid tier up and frankly paying this company feels worse that paying the taxman. 
-Finally, the amount of bugs I have bumped into make me wonder if they are running any form of automated tests when doing releases.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>This software is the worst part of my job, i resent it so much that i make sure that invoice and expense as little as possible just to avoid using it. Reconciling anything in a currency that differs from the current that my bank account is in is an utter pain. All my expenses are in dollars, but my account is in euros. This software is expensive and costs me days every month in which I should be doing my actual job/trade. Worst of all, migrating away from it looks like it is going to cost me days. Any features that look like they would save you any time are always on the next paid tier up and frankly paying this company feels worse that paying the taxman. Finally, the amount of bugs I have bumped into make me wonder if they are running any form of automated tests when doing releases.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>James Irving-Swift</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Facturación</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/68fa0f856d4a136f1e3cdc03</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>a16448e940dec55662d040077c3a404e</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Individual attention</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>The team responded to my request quickly and sensitively.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Jeanne Walker</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/68a59fa93441b8760a635fa6</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-07-14</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>15e59d09f12754e78cc7ecf820f7de85</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Friendly and professional.</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Friendly and professional.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Tomislav Autischer</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6874b4eac6f112b76c3c2d0f</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52.2" customHeight="1" s="5">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>8b3dd9cc047751737f2d2ccbba2aed85</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>I just started testing it and I can not…</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>I just started testing it and I can not even upload bank statements. Site is slo, don't even let me download templates, or access "import" area. No support at alI. Probably a way to force you to contract "premium support". Trying to figure it by myself.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>DAROAN</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Conciliación</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/681dd3035ed9ef6e1ce5ad52</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="39.55" customHeight="1" s="5">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2025-05-08</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>04738cdf072a3c177168527ef4b5d7f8</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>from 3 days I can not log in my account…</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>from 3 days I can not log in my account and from 3 days I am waiting for a help and nobody answer me I have a store I need to log in</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Michal</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/681c67b1fb809d37e6d254b9</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26.85" customHeight="1" s="5">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>0d233a4f61ec7ad8bdb11a996b987d36</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Terrible platform</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Terrible platform. One day to another change pricing over 100% and remove basic functions for customers of over 5 years.</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>George Parker</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/68189a92c96bc03b0b7e68bd</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="115.65" customHeight="1" s="5">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>3644da540c413c1a1b884788acb87afa</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Mediocre, very poor customer service, overpriced for what it is.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>I've been using Holded for years, and calling it mediocre is being generous. The software works more or less fine, but there are plenty of areas that could be improved. On top of that, they hardly release any useful updates anymore, only paid "gems".
-Recently, customer service has become nearly nonexistent — they reply after a week, if they even reply at all.
-Lastly, it's extremely expensive for what it offers. I keep using it out of laziness to migrate to better software, but it's going from bad to worse.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>I've been using Holded for years, and calling it mediocre is being generous. The software works more or less fine, but there are plenty of areas that could be improved. On top of that, they hardly release any useful updates anymore, only paid "gems". Recently, customer service has become nearly nonexistent, they reply after a week, if they even reply at all. Lastly, it's extremely expensive for what it offers. I keep using it out of laziness to migrate to better software, but it's going from bad to worse.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2/5 (Poor)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Фёдор</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fedor</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/67ed5578c792af1997f7f220</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26.85" customHeight="1" s="5">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>89dd39e15ddd06134d6d36dd5757c324</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>The software is great, but not good enough to make up for the lack of support</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>UPDATE: Sorry, but the issue has not been fully resolved, yet, as the reply to my review indicates.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>UPDATE: Sorry, but the issue has not been fully resolved, yet, as the reply to my review indicates. I've been using Holded since August 2024 and their service has gotten progressively worse. The software is good but the poor service taints everything. Customer Support is non existent. One of the things I learned today, only because an invoicing and number of users issue, is that if you have more Users than your plan allows, you're automatically blocked from using almost ALL the other functions you pay for in your subscription, I can't even make an invoice.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Luis Miguel Arenas</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Facturación</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/67c6df97d3aa8cb0c4e7704b</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26.85" customHeight="1" s="5">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>7dad9c5b2b57df952690726d17444623</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Great application</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Great application, it has helped our company a lot. Thank you very much.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Stephen James</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6681416a74edbc0d77a9bdb3</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="39.55" customHeight="1" s="5">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2024-06-19</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>aabd0bde2a0453946b63aca72c95b529</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Doesn't sync with bank account</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>I've been using Holded for about 6 months now.  It has not been able to to sync to my bank account for 3 of those months.  Despite raising complaints about it, nothing is done to resolve it</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>I've been using Holded for about 6 months now. It has not been able to to sync to my bank account for 3 of those months. Despite raising complaints about it, nothing is done to resolve it</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Anna</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6672a1a5ffaa37f32e5d1f08</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="52.2" customHeight="1" s="5">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2024-05-24</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>6517b226867788154d494c1d5a43e9dc</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Good product</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>This is the best book keeping and accounting software that I have used...by far. It does have some kinks, but I value the relatively high level of transparency in terms of what it is doing so it is easier to spot any issues.</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Phil</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/6650d91fa0b60b03607eedd7</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2024-04-14</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>251c8a908496fd4b551916dff089c327</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Delighted</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Delighted. Empowered.</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>5/5 (Excellent)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Namastecita</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/661c4b13d1353441d84637e9</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52.2" customHeight="1" s="5">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2024-01-29</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>e154f205cd7c1301b5f48fae4bdc6222</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Good product but its customer services…</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Good product but its customer services is a joke!. Its customer service is worse than any other big IT. When you get your account manager they dont even reply to your emails. Have a look at some other optioms in the market.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>1/5 (Bad)</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Michael Leather</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/reviews/65b79db5c2f1f89bd26afae4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/holded_reviews.xlsx
+++ b/holded_reviews.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviews" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reviews" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/holded_reviews.xlsx
+++ b/holded_reviews.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Precio</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Precio</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Precio</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
